--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1500,22 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1548,12 +1548,12 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1117 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2745,1129 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>4/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1363,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1474,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,17 +1518,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1518,13 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1585,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1696,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,17 +1756,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1740,13 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1807,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,33 +1875,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1968,7 +2016,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2079,7 +2127,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2155,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq51，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2140,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2148,10 +2196,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2190,7 +2250,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2301,7 +2361,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2412,7 +2472,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2523,7 +2583,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2634,7 +2694,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2805,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2866,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2856,7 +2916,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2977,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2967,7 +3027,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3088,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3078,7 +3138,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3199,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,7 +3249,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3310,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3300,7 +3360,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3421,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3471,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3532,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3522,7 +3582,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3643,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3637,7 +3697,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3758,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3752,7 +3812,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3873,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3862,12 +3922,809 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1933,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1990,33 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -2044,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2077,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2101,17 +2113,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2121,13 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2176,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq51，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq55，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2188,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2311,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2422,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2533,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2644,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2755,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,7 +2882,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,7 +2993,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3104,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,7 +3437,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3548,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3643,7 +3659,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,7 +3774,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3812,7 +3828,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3889,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3927,7 +3943,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -3988,7 +4004,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,7 +4119,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4157,7 +4173,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4234,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4329,7 +4345,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4383,7 +4399,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4460,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4498,7 +4514,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4575,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4670,7 +4686,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4728,6 +4744,236 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,14 +2128,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq55，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq62，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2405,32 +2405,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,33 +2466,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -2516,32 +2524,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2549,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2573,33 +2585,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2627,32 +2643,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2660,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2684,33 +2704,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -2738,32 +2762,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2771,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2795,33 +2823,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2921,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2993,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3071,32 +3103,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3104,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3128,17 +3164,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3148,13 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3182,32 +3222,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -3215,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3239,17 +3283,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3259,13 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3293,32 +3341,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3326,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3350,17 +3402,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3370,13 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3713,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3828,7 +3884,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3943,7 +3999,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4058,7 +4114,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4173,7 +4229,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4290,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4399,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4514,7 +4570,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4631,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4686,7 +4742,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4740,7 +4796,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4857,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4855,7 +4911,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4863,22 +4919,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4911,12 +4967,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4965,12 +5021,924 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>8/27</t>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>17/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,18 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1667,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3025,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3194,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,14 +3302,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -3313,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -3460,32 +3464,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3493,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,33 +3525,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3571,32 +3583,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3604,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3628,17 +3644,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3648,13 +3664,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3682,32 +3702,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3715,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3739,29 +3763,29 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3769,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -3797,32 +3821,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3830,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3854,17 +3882,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3874,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -3912,32 +3940,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3945,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3969,37 +4001,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -4027,32 +4059,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4060,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4084,17 +4120,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4104,17 +4140,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4142,32 +4178,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4175,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4199,17 +4239,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4219,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -4257,32 +4297,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4290,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4314,33 +4358,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4416,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4401,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4425,17 +4477,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4445,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4555,7 +4607,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4570,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4650,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4631,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4639,10 +4691,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4742,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4911,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4972,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5026,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5141,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5256,7 +5320,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5371,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5496,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5597,7 +5661,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5712,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5888,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5942,6 +6006,807 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>20/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>16/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,13 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2494,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2608,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2619,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2972,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3079,7 +3083,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3555,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3793,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4031,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4535,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4568,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4592,17 +4600,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4612,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4663,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq61，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4683,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4745,7 +4753,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4860,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4888,32 +4896,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4921,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4945,37 +4957,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5003,32 +5015,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5036,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,17 +5076,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5080,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5118,32 +5134,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5151,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,17 +5195,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5195,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5233,32 +5253,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5266,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5290,37 +5314,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5348,32 +5372,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -5381,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5405,17 +5433,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5425,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5463,32 +5491,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5496,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5520,17 +5552,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5540,13 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5574,32 +5610,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5607,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5631,17 +5671,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5651,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5801,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5776,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5891,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6002,7 +6042,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6113,7 +6153,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6228,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6343,7 +6383,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6458,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6573,7 +6613,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6688,7 +6728,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6793,17 +6833,695 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>16/27</t>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,18 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,18 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,22 +3552,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3797,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4933,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5106,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5456,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5501,24 +5509,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5528,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5577,12 +5585,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5620,12 +5628,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5647,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5696,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5729,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5762,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5786,17 +5798,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5806,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5844,32 +5856,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5877,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5901,17 +5917,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5921,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5959,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -5992,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,33 +6036,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6070,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6103,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6127,33 +6155,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6181,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6214,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6238,17 +6274,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6258,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6296,32 +6332,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6329,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6353,37 +6393,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6483,7 +6523,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6498,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6613,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6728,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6843,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7015,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,7 +7281,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7467,7 +7507,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7511,17 +7551,592 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>18/28</t>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,14 +3433,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,14 +4266,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4623,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6342,12 +6342,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6451,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6484,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6508,17 +6512,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6528,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6566,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6599,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,37 +6631,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6681,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6714,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6738,17 +6750,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6758,7 +6770,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6768,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6829,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6853,37 +6869,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6927,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6944,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6952,10 +6968,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7055,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7109,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7137,32 +7169,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7170,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7194,33 +7230,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7335,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7507,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7561,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7676,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7791,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7906,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7967,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8011,17 +8051,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8131,12 +8171,702 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,13 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,7 +2498,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2504,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3394,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3870,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4519,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/28</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4699,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4754,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4985,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5222,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,7 +5465,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6607,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6845,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6932,7 +6936,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq61，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6960,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7015,7 +7019,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7054,32 +7058,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7087,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,17 +7119,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7131,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7288,32 +7296,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7321,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,17 +7357,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7365,17 +7377,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7403,32 +7415,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7436,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,17 +7476,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7480,13 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7514,32 +7534,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7547,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7571,17 +7595,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7591,17 +7615,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -7629,32 +7653,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -7662,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7686,17 +7714,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7706,7 +7734,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7716,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7744,32 +7772,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7777,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7801,17 +7833,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7821,17 +7853,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7946,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8122,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8237,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8291,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8467,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8521,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8697,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8759,22 +8791,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8807,12 +8839,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8826,47 +8858,618 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
+      <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>124.0</t>
         </is>
       </c>
-      <c r="AC71" s="2" t="inlineStr">
+      <c r="AC72" s="2" t="inlineStr">
         <is>
           <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,14 +3318,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,14 +6293,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,17 +6417,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7782,24 +7782,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7891,32 +7891,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7924,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,17 +7952,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7968,17 +7972,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8006,32 +8010,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8039,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8071,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8083,12 +8091,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8121,32 +8129,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8154,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8190,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8198,17 +8210,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -8236,32 +8248,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8269,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8309,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8313,17 +8329,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8367,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8384,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8428,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8428,12 +8448,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8499,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8614,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8729,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8844,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8955,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9070,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9185,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9300,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9415,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9473,6 +9493,811 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>27/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,22 +3437,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -8258,24 +8258,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8324,22 +8324,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8377,24 +8377,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8486,32 +8486,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8519,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,17 +8547,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8563,17 +8567,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -8601,32 +8605,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8634,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8658,17 +8666,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8678,12 +8686,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8749,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8831,12 +8839,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq42，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8864,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,10 +8880,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -8975,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9090,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9205,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9320,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9435,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9550,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9665,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9780,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9895,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10010,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10125,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10240,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10298,6 +10322,236 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7258,17 +7258,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8724,32 +8724,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8757,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,37 +8785,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8848,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq42，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8872,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8966,32 +8970,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8999,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9023,17 +9031,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9043,17 +9051,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -9081,32 +9089,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -9114,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9138,17 +9150,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9158,17 +9170,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9344,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9459,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9574,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9628,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9804,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9858,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10034,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10149,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10203,7 +10215,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10318,7 +10330,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10494,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10552,6 +10564,696 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>26/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,22 +3675,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7253,14 +7253,14 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9046,14 +9046,14 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -9099,24 +9099,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -9208,32 +9208,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9241,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9265,37 +9269,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9323,32 +9327,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9356,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9380,37 +9388,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9525,7 +9533,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9553,32 +9561,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9586,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9610,17 +9622,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9630,17 +9642,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -9668,32 +9680,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9701,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,17 +9741,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9745,17 +9761,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -9783,32 +9799,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9816,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9840,37 +9860,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9985,7 +10005,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10161,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10276,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10330,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10506,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10621,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10675,7 +10695,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10790,7 +10810,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10966,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11081,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11196,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11250,7 +11270,923 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>125.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,17 +4508,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8329,17 +8329,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9690,24 +9690,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9756,22 +9756,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9809,24 +9809,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10033,32 +10033,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10066,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10090,32 +10094,32 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10148,32 +10152,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10181,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10205,37 +10213,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10350,7 +10358,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -10378,32 +10386,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10411,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10435,17 +10447,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10455,17 +10467,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -10493,32 +10505,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10526,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10550,17 +10566,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10570,17 +10586,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -10608,32 +10624,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10641,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10665,17 +10685,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10685,17 +10705,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10871,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10986,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11101,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11216,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11331,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11385,7 +11405,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11557,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11611,7 +11631,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11787,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11902,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12017,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12071,7 +12091,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -12079,22 +12099,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12127,12 +12147,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12146,47 +12166,852 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W100" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X100" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y100" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z100" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>125.7</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
         <is>
           <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>27/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>127.3</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7615,17 +7615,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7853,17 +7853,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9289,17 +9289,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -10634,24 +10634,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10743,32 +10743,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10776,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10800,17 +10804,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10820,7 +10824,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10858,32 +10862,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10891,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10915,17 +10923,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10935,17 +10943,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -10973,32 +10981,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11006,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11030,17 +11042,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11050,12 +11062,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11088,32 +11100,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11121,7 +11137,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11145,17 +11161,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11165,12 +11181,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11203,32 +11219,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11236,7 +11256,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11260,17 +11280,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11280,17 +11300,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11425,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -11433,12 +11453,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq56，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -11466,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11474,10 +11494,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q93" s="2" t="inlineStr"/>
-      <c r="R93" s="2" t="inlineStr"/>
-      <c r="S93" s="2" t="inlineStr"/>
-      <c r="T93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11577,7 +11613,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11616,7 +11652,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11631,7 +11667,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -11659,32 +11695,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11692,7 +11732,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11716,17 +11756,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11736,17 +11776,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11889,32 +11929,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11922,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11946,17 +11990,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11966,17 +12010,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12091,7 +12135,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12196,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12206,7 +12250,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12311,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12321,7 +12365,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12426,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12497,7 +12541,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12612,7 +12656,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12727,7 +12771,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12781,7 +12825,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12886,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12957,7 +13001,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13011,7 +13055,237 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-01-浦东35路.xlsx
+++ b/data/export/2026-10-01-浦东35路.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9170,17 +9170,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9880,17 +9880,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11705,24 +11705,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -11814,32 +11814,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11847,7 +11851,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11871,17 +11875,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11891,17 +11895,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -11939,24 +11943,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11966,7 +11970,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12015,12 +12019,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -12048,32 +12052,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12081,7 +12089,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12105,17 +12113,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12125,17 +12133,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -12163,12 +12171,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -12196,7 +12204,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12204,10 +12212,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="2" t="inlineStr"/>
-      <c r="S99" s="2" t="inlineStr"/>
-      <c r="T99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12278,32 +12302,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12311,7 +12339,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12335,17 +12363,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12355,17 +12383,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -12393,32 +12421,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12426,7 +12458,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12450,17 +12482,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12470,17 +12502,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12573,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12656,7 +12688,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12771,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12825,7 +12857,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12918,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -13001,7 +13033,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13116,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13231,7 +13263,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
